--- a/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-01-2026.xlsx
+++ b/Compititor's_Price/Celotex_Prices/Celotex_Prices_01-01-2026.xlsx
@@ -1125,7 +1125,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>£20.97</t>
+          <t>Error: ('Connection aborted.', RemoteDisconnected('Remote end closed connection without response'))</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>£23.83</t>
+          <t>Error: HTTPSConnectionPool(host='www.insulation-online.com', port=443): Read timed out.</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>£52.32</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£38.56 Pre Sale Price-£40.83</t>
         </is>
       </c>
     </row>
@@ -2393,7 +2393,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>£40.59</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>£42.88</t>
+          <t>£43.79</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>£42.88</t>
+          <t>£43.64</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>£40.53</t>
+          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>£42.88</t>
+          <t>£43.08</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
